--- a/Plannewplant.xlsx
+++ b/Plannewplant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ABBFC75-D005-4FBE-B71E-A1C7D9B7780C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8851F8DE-CFF4-4D44-B0C0-8BC4282255F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{E10731B5-8D57-4A48-9395-53C149A1FEF2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>กิจการ</t>
   </si>
@@ -84,9 +84,6 @@
     <t>ตะวันออก</t>
   </si>
   <si>
-    <t>VS คอนกรีต 2</t>
-  </si>
-  <si>
     <t>ปราจีนบุรี</t>
   </si>
   <si>
@@ -214,13 +211,25 @@
   </si>
   <si>
     <t>ผู้ว่าลงนามอนุมัติผ่อนปรนพื้นที่เพื่อออก รง.4 แล้ว ส่งหนังสือให้ อบต.เพื่อติดประกาศทั้งจังหวัด</t>
+  </si>
+  <si>
+    <t>overhaul เครื่องจักร</t>
+  </si>
+  <si>
+    <t>วี.เอส.คอนกรีต 3 ลาดตะเคียน (Type X)</t>
+  </si>
+  <si>
+    <t>วี.เอส.คอนกรีต 2</t>
+  </si>
+  <si>
+    <t>AUG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,11 +249,6 @@
       <sz val="9"/>
       <name val="SCG"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -347,7 +351,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -718,11 +732,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CDBF296-9CAB-4502-8B20-17EB50A83420}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.08984375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.26953125" style="16" customWidth="1"/>
     <col min="4" max="4" width="5.90625" style="19" customWidth="1"/>
     <col min="5" max="5" width="30.54296875" style="18" bestFit="1" customWidth="1"/>
@@ -746,16 +760,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -772,16 +786,16 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -798,13 +812,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3" s="9"/>
     </row>
@@ -822,16 +836,16 @@
         <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -839,22 +853,22 @@
         <v>17</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="9"/>
     </row>
@@ -863,25 +877,25 @@
         <v>17</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="D6" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -889,112 +903,112 @@
         <v>17</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>6</v>
@@ -1004,86 +1018,117 @@
         <v>9</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H13" xr:uid="{3B84A060-731B-4AC7-B1A2-328C84BA83E3}"/>
-  <conditionalFormatting sqref="F8 F1:F6 F11:F12 F14:F1048576">
+  <conditionalFormatting sqref="F8 F1:F6 F11:F12 F15:F1048576">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
+  <conditionalFormatting sqref="F9:F10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F10">
+  <conditionalFormatting sqref="F7">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
+  <conditionalFormatting sqref="F13">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
+  <conditionalFormatting sqref="F9">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
+  <conditionalFormatting sqref="F14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"OPEN"</formula>
     </cfRule>
